--- a/development/one_file_rosetta_output/DRUP01340014T_rosetta.xlsx
+++ b/development/one_file_rosetta_output/DRUP01340014T_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E432"/>
+  <dimension ref="A1:F432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -510,7 +519,10 @@
       <c r="D3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="4">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -566,7 +578,10 @@
       <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -594,7 +609,10 @@
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -657,7 +675,10 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -718,9 +739,12 @@
         </is>
       </c>
       <c r="D7" s="4">
+        <v>2</v>
+      </c>
+      <c r="E7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -783,7 +807,10 @@
       <c r="D8" s="4">
         <v>2</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -846,7 +873,10 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -874,7 +904,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -902,7 +935,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -958,7 +994,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -986,7 +1025,10 @@
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1042,7 +1084,10 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1068,9 +1113,12 @@
         </is>
       </c>
       <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1141,7 +1189,10 @@
       <c r="D16" s="4">
         <v>2</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1210,9 +1261,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1283,7 +1337,10 @@
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1311,7 +1368,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1337,9 +1397,12 @@
         </is>
       </c>
       <c r="D20" s="4">
+        <v>4</v>
+      </c>
+      <c r="E20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1393,9 +1456,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>4</v>
+      </c>
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1449,9 +1515,12 @@
         </is>
       </c>
       <c r="D22" s="4">
+        <v>4</v>
+      </c>
+      <c r="E22" s="4">
         <v>2</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1505,9 +1574,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>4</v>
+      </c>
+      <c r="E23" s="4">
         <v>3</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1561,9 +1633,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>3</v>
+      </c>
+      <c r="E24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1624,9 +1699,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>3</v>
+      </c>
+      <c r="E25" s="4">
         <v>2</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1687,9 +1765,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>2</v>
+      </c>
+      <c r="E26" s="4">
         <v>1</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1758,9 +1839,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>3</v>
+      </c>
+      <c r="E27" s="4">
         <v>1</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1831,7 +1915,10 @@
       <c r="D28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="4">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1909,7 +1996,10 @@
       <c r="D29" s="4">
         <v>1</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="4">
+        <v>1</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2023,9 +2113,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>3</v>
+      </c>
+      <c r="E30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2079,9 +2172,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4">
         <v>1</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2107,9 +2203,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>2</v>
+      </c>
+      <c r="E32" s="4">
         <v>1</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2180,7 +2279,10 @@
       <c r="D33" s="4">
         <v>2</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="4">
+        <v>2</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2249,9 +2351,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>2</v>
+      </c>
+      <c r="E34" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2327,9 +2432,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>3</v>
+      </c>
+      <c r="E35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2357,7 +2465,10 @@
       <c r="D36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2443,7 +2554,10 @@
       <c r="D37" s="4">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2529,7 +2643,10 @@
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2557,7 +2674,10 @@
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2583,9 +2703,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>2</v>
+      </c>
+      <c r="E40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2684,9 +2807,12 @@
         </is>
       </c>
       <c r="D41" s="4">
+        <v>3</v>
+      </c>
+      <c r="E41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2792,9 +2918,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>3</v>
+      </c>
+      <c r="E42" s="4">
         <v>2</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2902,7 +3031,10 @@
       <c r="D43" s="4">
         <v>3</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>3</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3008,9 +3140,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>2</v>
+      </c>
+      <c r="E44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3118,7 +3253,10 @@
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3144,9 +3282,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3260,9 +3401,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>5</v>
+      </c>
+      <c r="E47" s="4">
         <v>2</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3376,9 +3520,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>5</v>
+      </c>
+      <c r="E48" s="4">
         <v>3</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3494,7 +3641,10 @@
       <c r="D49" s="4">
         <v>1</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="4">
+        <v>1</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3522,7 +3672,10 @@
       <c r="D50" s="4">
         <v>1</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="4">
+        <v>1</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3548,9 +3701,12 @@
         </is>
       </c>
       <c r="D51" s="4">
+        <v>2</v>
+      </c>
+      <c r="E51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3576,9 +3732,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>2</v>
+      </c>
+      <c r="E52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3634,7 +3793,10 @@
       <c r="D53" s="4">
         <v>2</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="4">
+        <v>2</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3690,7 +3852,10 @@
       <c r="D54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="4">
+        <v>1</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3746,7 +3911,10 @@
       <c r="D55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E55" s="4">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3807,9 +3975,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>5</v>
+      </c>
+      <c r="E56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3870,9 +4041,12 @@
         </is>
       </c>
       <c r="D57" s="4">
+        <v>5</v>
+      </c>
+      <c r="E57" s="4">
         <v>2</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3933,9 +4107,12 @@
         </is>
       </c>
       <c r="D58" s="4">
+        <v>5</v>
+      </c>
+      <c r="E58" s="4">
         <v>3</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3998,7 +4175,10 @@
       <c r="D59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4067,9 +4247,12 @@
         </is>
       </c>
       <c r="D60" s="4">
+        <v>2</v>
+      </c>
+      <c r="E60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4097,7 +4280,10 @@
       <c r="D61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="4">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4125,7 +4311,10 @@
       <c r="D62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="4">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4151,9 +4340,12 @@
         </is>
       </c>
       <c r="D63" s="4">
+        <v>2</v>
+      </c>
+      <c r="E63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4181,7 +4373,10 @@
       <c r="D64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="4">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4267,7 +4462,10 @@
       <c r="D65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4368,7 +4566,10 @@
       <c r="D66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4394,9 +4595,12 @@
         </is>
       </c>
       <c r="D67" s="4">
+        <v>2</v>
+      </c>
+      <c r="E67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4504,7 +4708,10 @@
       <c r="D68" s="4">
         <v>2</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="4">
+        <v>2</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4612,7 +4819,10 @@
       <c r="D69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E69" s="4">
+        <v>1</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4640,7 +4850,10 @@
       <c r="D70" s="4">
         <v>1</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="4">
+        <v>1</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4668,7 +4881,10 @@
       <c r="D71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4696,7 +4912,10 @@
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4752,7 +4971,10 @@
       <c r="D73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4830,7 +5052,10 @@
       <c r="D74" s="4">
         <v>1</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4916,7 +5141,10 @@
       <c r="D75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4944,7 +5172,10 @@
       <c r="D76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4972,7 +5203,10 @@
       <c r="D77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5080,7 +5314,10 @@
       <c r="D78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5134,9 +5371,12 @@
         </is>
       </c>
       <c r="D79" s="4">
+        <v>4</v>
+      </c>
+      <c r="E79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5164,7 +5404,10 @@
       <c r="D80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="4">
+        <v>1</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5225,9 +5468,12 @@
         </is>
       </c>
       <c r="D81" s="4">
+        <v>3</v>
+      </c>
+      <c r="E81" s="4">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5305,7 +5551,10 @@
       <c r="D82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5383,7 +5632,10 @@
       <c r="D83" s="4">
         <v>1</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5467,9 +5719,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>2</v>
+      </c>
+      <c r="E84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5562,7 +5817,10 @@
       <c r="D85" s="4">
         <v>1</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="4">
+        <v>1</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5663,7 +5921,10 @@
       <c r="D86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5771,7 +6032,10 @@
       <c r="D87" s="4">
         <v>1</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5885,9 +6149,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>65</v>
+      </c>
+      <c r="E88" s="4">
         <v>1</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5941,9 +6208,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>65</v>
+      </c>
+      <c r="E89" s="4">
         <v>2</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5997,9 +6267,12 @@
         </is>
       </c>
       <c r="D90" s="4">
+        <v>65</v>
+      </c>
+      <c r="E90" s="4">
         <v>3</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6053,9 +6326,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>65</v>
+      </c>
+      <c r="E91" s="4">
         <v>4</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6109,9 +6385,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>65</v>
+      </c>
+      <c r="E92" s="4">
         <v>5</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6167,7 +6446,10 @@
       <c r="D93" s="4">
         <v>1</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="4">
+        <v>1</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6193,9 +6475,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>12</v>
+      </c>
+      <c r="E94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6256,9 +6541,12 @@
         </is>
       </c>
       <c r="D95" s="4">
+        <v>12</v>
+      </c>
+      <c r="E95" s="4">
         <v>2</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6319,9 +6607,12 @@
         </is>
       </c>
       <c r="D96" s="4">
+        <v>12</v>
+      </c>
+      <c r="E96" s="4">
         <v>3</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6382,9 +6673,12 @@
         </is>
       </c>
       <c r="D97" s="4">
+        <v>12</v>
+      </c>
+      <c r="E97" s="4">
         <v>4</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6445,9 +6739,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>12</v>
+      </c>
+      <c r="E98" s="4">
         <v>5</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6508,9 +6805,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>2</v>
+      </c>
+      <c r="E99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6538,7 +6838,10 @@
       <c r="D100" s="4">
         <v>1</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="4">
+        <v>1</v>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6599,9 +6902,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>2</v>
+      </c>
+      <c r="E101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6672,7 +6978,10 @@
       <c r="D102" s="4">
         <v>1</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="4">
+        <v>1</v>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6743,7 +7052,10 @@
       <c r="D103" s="4">
         <v>1</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="4">
+        <v>1</v>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6827,9 +7139,12 @@
         </is>
       </c>
       <c r="D104" s="4">
+        <v>2</v>
+      </c>
+      <c r="E104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6922,7 +7237,10 @@
       <c r="D105" s="4">
         <v>2</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="4">
+        <v>2</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7015,7 +7333,10 @@
       <c r="D106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7123,7 +7444,10 @@
       <c r="D107" s="4">
         <v>1</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="4">
+        <v>1</v>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7177,9 +7501,12 @@
         </is>
       </c>
       <c r="D108" s="4">
+        <v>2</v>
+      </c>
+      <c r="E108" s="4">
         <v>1</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7205,9 +7532,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>2</v>
+      </c>
+      <c r="E109" s="4">
         <v>1</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7283,9 +7613,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>2</v>
+      </c>
+      <c r="E110" s="4">
         <v>1</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7311,9 +7644,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>2</v>
+      </c>
+      <c r="E111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7404,9 +7740,12 @@
         </is>
       </c>
       <c r="D112" s="4">
+        <v>2</v>
+      </c>
+      <c r="E112" s="4">
         <v>1</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7497,9 +7836,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>4</v>
+      </c>
+      <c r="E113" s="4">
         <v>1</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7598,9 +7940,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>4</v>
+      </c>
+      <c r="E114" s="4">
         <v>2</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7699,9 +8044,12 @@
         </is>
       </c>
       <c r="D115" s="4">
+        <v>4</v>
+      </c>
+      <c r="E115" s="4">
         <v>3</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7802,7 +8150,10 @@
       <c r="D116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E116" s="4">
+        <v>1</v>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7910,7 +8261,10 @@
       <c r="D117" s="4">
         <v>1</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="E117" s="4">
+        <v>1</v>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7936,9 +8290,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>3</v>
+      </c>
+      <c r="E118" s="4">
         <v>1</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7964,9 +8321,12 @@
         </is>
       </c>
       <c r="D119" s="4">
+        <v>2</v>
+      </c>
+      <c r="E119" s="4">
         <v>1</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8029,7 +8389,10 @@
       <c r="D120" s="4">
         <v>2</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="4">
+        <v>2</v>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8090,9 +8453,12 @@
         </is>
       </c>
       <c r="D121" s="4">
+        <v>2</v>
+      </c>
+      <c r="E121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8120,7 +8486,10 @@
       <c r="D122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="4">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8191,7 +8560,10 @@
       <c r="D123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8219,7 +8591,10 @@
       <c r="D124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8297,7 +8672,10 @@
       <c r="D125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="4">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8325,7 +8703,10 @@
       <c r="D126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8353,7 +8734,10 @@
       <c r="D127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="4">
+        <v>1</v>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8452,9 +8836,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>2</v>
+      </c>
+      <c r="E128" s="4">
         <v>1</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8480,9 +8867,12 @@
         </is>
       </c>
       <c r="D129" s="4">
+        <v>2</v>
+      </c>
+      <c r="E129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8588,9 +8978,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>2</v>
+      </c>
+      <c r="E130" s="4">
         <v>1</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8616,9 +9009,12 @@
         </is>
       </c>
       <c r="D131" s="4">
+        <v>2</v>
+      </c>
+      <c r="E131" s="4">
         <v>1</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8726,7 +9122,10 @@
       <c r="D132" s="4">
         <v>2</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="4">
+        <v>2</v>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8832,9 +9231,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>3</v>
+      </c>
+      <c r="E133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8948,9 +9350,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>2</v>
+      </c>
+      <c r="E134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9066,7 +9471,10 @@
       <c r="D135" s="4">
         <v>2</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="4">
+        <v>2</v>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9180,9 +9588,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>4</v>
+      </c>
+      <c r="E136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9303,9 +9714,12 @@
         </is>
       </c>
       <c r="D137" s="4">
+        <v>4</v>
+      </c>
+      <c r="E137" s="4">
         <v>2</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9426,9 +9840,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>4</v>
+      </c>
+      <c r="E138" s="4">
         <v>3</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9549,9 +9966,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>5</v>
+      </c>
+      <c r="E139" s="4">
         <v>1</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9672,9 +10092,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>4</v>
+      </c>
+      <c r="E140" s="4">
         <v>1</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9795,9 +10218,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>4</v>
+      </c>
+      <c r="E141" s="4">
         <v>1</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9858,9 +10284,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>4</v>
+      </c>
+      <c r="E142" s="4">
         <v>2</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9923,7 +10352,10 @@
       <c r="D143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="4">
+        <v>1</v>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9992,9 +10424,12 @@
         </is>
       </c>
       <c r="D144" s="4">
+        <v>6</v>
+      </c>
+      <c r="E144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10063,9 +10498,12 @@
         </is>
       </c>
       <c r="D145" s="4">
+        <v>2</v>
+      </c>
+      <c r="E145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10136,7 +10574,10 @@
       <c r="D146" s="4">
         <v>2</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="4">
+        <v>2</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10207,7 +10648,10 @@
       <c r="D147" s="4">
         <v>1</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="4">
+        <v>1</v>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10285,7 +10729,10 @@
       <c r="D148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="4">
+        <v>1</v>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10363,7 +10810,10 @@
       <c r="D149" s="4">
         <v>1</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="E149" s="4">
+        <v>1</v>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10391,7 +10841,10 @@
       <c r="D150" s="4">
         <v>1</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="4">
+        <v>1</v>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10484,7 +10937,10 @@
       <c r="D151" s="4">
         <v>1</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="4">
+        <v>1</v>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10510,9 +10966,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>2</v>
+      </c>
+      <c r="E152" s="4">
         <v>1</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10540,7 +10999,10 @@
       <c r="D153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="E153" s="4">
+        <v>1</v>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10646,9 +11108,12 @@
         </is>
       </c>
       <c r="D154" s="4">
+        <v>4</v>
+      </c>
+      <c r="E154" s="4">
         <v>1</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10754,9 +11219,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>4</v>
+      </c>
+      <c r="E155" s="4">
         <v>2</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10864,7 +11332,10 @@
       <c r="D156" s="4">
         <v>1</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="4">
+        <v>1</v>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10978,9 +11449,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>2</v>
+      </c>
+      <c r="E157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11006,9 +11480,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>3</v>
+      </c>
+      <c r="E158" s="4">
         <v>1</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11122,9 +11599,12 @@
         </is>
       </c>
       <c r="D159" s="4">
+        <v>3</v>
+      </c>
+      <c r="E159" s="4">
         <v>2</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11240,7 +11720,10 @@
       <c r="D160" s="4">
         <v>3</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="4">
+        <v>3</v>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11356,7 +11839,10 @@
       <c r="D161" s="4">
         <v>1</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E161" s="4">
+        <v>1</v>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11477,9 +11963,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>3</v>
+      </c>
+      <c r="E162" s="4">
         <v>1</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11600,9 +12089,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>3</v>
+      </c>
+      <c r="E163" s="4">
         <v>2</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11723,9 +12215,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>22</v>
+      </c>
+      <c r="E164" s="4">
         <v>1</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11779,9 +12274,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>22</v>
+      </c>
+      <c r="E165" s="4">
         <v>2</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11835,9 +12333,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>22</v>
+      </c>
+      <c r="E166" s="4">
         <v>3</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11891,9 +12392,12 @@
         </is>
       </c>
       <c r="D167" s="4">
+        <v>22</v>
+      </c>
+      <c r="E167" s="4">
         <v>4</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11947,9 +12451,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>22</v>
+      </c>
+      <c r="E168" s="4">
         <v>5</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12005,7 +12512,10 @@
       <c r="D169" s="4">
         <v>1</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E169" s="4">
+        <v>1</v>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12031,9 +12541,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>2</v>
+      </c>
+      <c r="E170" s="4">
         <v>1</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12096,7 +12609,10 @@
       <c r="D171" s="4">
         <v>1</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="4">
+        <v>1</v>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12167,7 +12683,10 @@
       <c r="D172" s="4">
         <v>1</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E172" s="4">
+        <v>1</v>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12195,7 +12714,10 @@
       <c r="D173" s="4">
         <v>1</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E173" s="4">
+        <v>1</v>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12223,7 +12745,10 @@
       <c r="D174" s="4">
         <v>1</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="4">
+        <v>1</v>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12322,9 +12847,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>2</v>
+      </c>
+      <c r="E175" s="4">
         <v>1</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12432,7 +12960,10 @@
       <c r="D176" s="4">
         <v>1</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="4">
+        <v>1</v>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12538,9 +13069,12 @@
         </is>
       </c>
       <c r="D177" s="4">
+        <v>2</v>
+      </c>
+      <c r="E177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12656,7 +13190,10 @@
       <c r="D178" s="4">
         <v>2</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E178" s="4">
+        <v>2</v>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12772,7 +13309,10 @@
       <c r="D179" s="4">
         <v>1</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E179" s="4">
+        <v>1</v>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12886,9 +13426,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>6</v>
+      </c>
+      <c r="E180" s="4">
         <v>1</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13002,9 +13545,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>6</v>
+      </c>
+      <c r="E181" s="4">
         <v>2</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13118,9 +13664,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>6</v>
+      </c>
+      <c r="E182" s="4">
         <v>3</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13236,7 +13785,10 @@
       <c r="D183" s="4">
         <v>1</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E183" s="4">
+        <v>1</v>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13359,7 +13911,10 @@
       <c r="D184" s="4">
         <v>1</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="4">
+        <v>1</v>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13415,7 +13970,10 @@
       <c r="D185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="4">
+        <v>1</v>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13469,9 +14027,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>3</v>
+      </c>
+      <c r="E186" s="4">
         <v>1</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13525,9 +14086,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>3</v>
+      </c>
+      <c r="E187" s="4">
         <v>2</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13583,7 +14147,10 @@
       <c r="D188" s="4">
         <v>3</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="4">
+        <v>3</v>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13639,7 +14206,10 @@
       <c r="D189" s="4">
         <v>1</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="4">
+        <v>1</v>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13695,7 +14265,10 @@
       <c r="D190" s="4">
         <v>1</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="4">
+        <v>1</v>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13751,7 +14324,10 @@
       <c r="D191" s="4">
         <v>1</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="4">
+        <v>1</v>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13807,7 +14383,10 @@
       <c r="D192" s="4">
         <v>1</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="4">
+        <v>1</v>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13863,7 +14442,10 @@
       <c r="D193" s="4">
         <v>1</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="4">
+        <v>1</v>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13917,9 +14499,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>5</v>
+      </c>
+      <c r="E194" s="4">
         <v>1</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13973,9 +14558,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>5</v>
+      </c>
+      <c r="E195" s="4">
         <v>2</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14029,9 +14617,12 @@
         </is>
       </c>
       <c r="D196" s="4">
+        <v>5</v>
+      </c>
+      <c r="E196" s="4">
         <v>3</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14085,9 +14676,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>5</v>
+      </c>
+      <c r="E197" s="4">
         <v>4</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14143,7 +14737,10 @@
       <c r="D198" s="4">
         <v>5</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="4">
+        <v>5</v>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14197,9 +14794,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>2</v>
+      </c>
+      <c r="E199" s="4">
         <v>1</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14271,7 +14871,10 @@
       <c r="D200" s="4">
         <v>2</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E200" s="4">
+        <v>2</v>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14343,7 +14946,10 @@
       <c r="D201" s="4">
         <v>1</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="E201" s="4">
+        <v>1</v>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14406,7 +15012,10 @@
       <c r="D202" s="4">
         <v>1</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="E202" s="4">
+        <v>1</v>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14467,9 +15076,12 @@
         </is>
       </c>
       <c r="D203" s="4">
+        <v>6</v>
+      </c>
+      <c r="E203" s="4">
         <v>1</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14530,9 +15142,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>6</v>
+      </c>
+      <c r="E204" s="4">
         <v>2</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14593,9 +15208,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>6</v>
+      </c>
+      <c r="E205" s="4">
         <v>3</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14656,9 +15274,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>6</v>
+      </c>
+      <c r="E206" s="4">
         <v>4</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14719,9 +15340,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>6</v>
+      </c>
+      <c r="E207" s="4">
         <v>5</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14784,7 +15408,10 @@
       <c r="D208" s="4">
         <v>6</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="4">
+        <v>6</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14845,9 +15472,12 @@
         </is>
       </c>
       <c r="D209" s="4">
+        <v>3</v>
+      </c>
+      <c r="E209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14916,9 +15546,12 @@
         </is>
       </c>
       <c r="D210" s="4">
+        <v>3</v>
+      </c>
+      <c r="E210" s="4">
         <v>2</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14989,7 +15622,10 @@
       <c r="D211" s="4">
         <v>3</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="E211" s="4">
+        <v>3</v>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15058,9 +15694,12 @@
         </is>
       </c>
       <c r="D212" s="4">
+        <v>132</v>
+      </c>
+      <c r="E212" s="4">
         <v>1</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15181,9 +15820,12 @@
         </is>
       </c>
       <c r="D213" s="4">
+        <v>132</v>
+      </c>
+      <c r="E213" s="4">
         <v>2</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15364,9 +16006,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>132</v>
+      </c>
+      <c r="E214" s="4">
         <v>3</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15487,9 +16132,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>132</v>
+      </c>
+      <c r="E215" s="4">
         <v>4</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15610,9 +16258,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>132</v>
+      </c>
+      <c r="E216" s="4">
         <v>5</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15748,9 +16399,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>132</v>
+      </c>
+      <c r="E217" s="4">
         <v>6</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15931,9 +16585,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>132</v>
+      </c>
+      <c r="E218" s="4">
         <v>7</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16062,9 +16719,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>132</v>
+      </c>
+      <c r="E219" s="4">
         <v>8</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16208,9 +16868,12 @@
         </is>
       </c>
       <c r="D220" s="4">
+        <v>132</v>
+      </c>
+      <c r="E220" s="4">
         <v>9</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16346,9 +17009,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>132</v>
+      </c>
+      <c r="E221" s="4">
         <v>10</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16477,9 +17143,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>132</v>
+      </c>
+      <c r="E222" s="4">
         <v>11</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16608,9 +17277,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>132</v>
+      </c>
+      <c r="E223" s="4">
         <v>12</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16754,9 +17426,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>132</v>
+      </c>
+      <c r="E224" s="4">
         <v>13</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16870,9 +17545,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>132</v>
+      </c>
+      <c r="E225" s="4">
         <v>14</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17001,9 +17679,12 @@
         </is>
       </c>
       <c r="D226" s="4">
+        <v>132</v>
+      </c>
+      <c r="E226" s="4">
         <v>15</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17147,9 +17828,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>132</v>
+      </c>
+      <c r="E227" s="4">
         <v>16</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17300,9 +17984,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>132</v>
+      </c>
+      <c r="E228" s="4">
         <v>17</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17461,9 +18148,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>132</v>
+      </c>
+      <c r="E229" s="4">
         <v>18</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17592,9 +18282,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>132</v>
+      </c>
+      <c r="E230" s="4">
         <v>19</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17685,9 +18378,12 @@
         </is>
       </c>
       <c r="D231" s="4">
+        <v>132</v>
+      </c>
+      <c r="E231" s="4">
         <v>20</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17801,9 +18497,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>2</v>
+      </c>
+      <c r="E232" s="4">
         <v>1</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17881,7 +18580,10 @@
       <c r="D233" s="4">
         <v>2</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="E233" s="4">
+        <v>2</v>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17957,9 +18659,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>4</v>
+      </c>
+      <c r="E234" s="4">
         <v>1</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18020,9 +18725,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>4</v>
+      </c>
+      <c r="E235" s="4">
         <v>2</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18083,9 +18791,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>4</v>
+      </c>
+      <c r="E236" s="4">
         <v>3</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18148,7 +18859,10 @@
       <c r="D237" s="4">
         <v>4</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="E237" s="4">
+        <v>4</v>
+      </c>
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18211,7 +18925,10 @@
       <c r="D238" s="4">
         <v>1</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="E238" s="4">
+        <v>1</v>
+      </c>
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18282,7 +18999,10 @@
       <c r="D239" s="4">
         <v>1</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="E239" s="4">
+        <v>1</v>
+      </c>
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18360,7 +19080,10 @@
       <c r="D240" s="4">
         <v>1</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="E240" s="4">
+        <v>1</v>
+      </c>
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18421,9 +19144,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>3</v>
+      </c>
+      <c r="E241" s="4">
         <v>1</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18507,9 +19233,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>3</v>
+      </c>
+      <c r="E242" s="4">
         <v>2</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18595,7 +19324,10 @@
       <c r="D243" s="4">
         <v>3</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="4">
+        <v>3</v>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18711,7 +19443,10 @@
       <c r="D244" s="4">
         <v>1</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="4">
+        <v>1</v>
+      </c>
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18772,9 +19507,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>2</v>
+      </c>
+      <c r="E245" s="4">
         <v>1</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18845,7 +19583,10 @@
       <c r="D246" s="4">
         <v>2</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="E246" s="4">
+        <v>2</v>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18916,7 +19657,10 @@
       <c r="D247" s="4">
         <v>1</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="E247" s="4">
+        <v>1</v>
+      </c>
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18986,9 +19730,12 @@
         </is>
       </c>
       <c r="D248" s="4">
+        <v>3</v>
+      </c>
+      <c r="E248" s="4">
         <v>1</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19057,9 +19804,12 @@
         </is>
       </c>
       <c r="D249" s="4">
+        <v>3</v>
+      </c>
+      <c r="E249" s="4">
         <v>2</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19130,7 +19880,10 @@
       <c r="D250" s="4">
         <v>3</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="E250" s="4">
+        <v>3</v>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19193,7 +19946,10 @@
       <c r="D251" s="4">
         <v>1</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="E251" s="4">
+        <v>1</v>
+      </c>
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19277,9 +20033,12 @@
         </is>
       </c>
       <c r="D252" s="4">
+        <v>6</v>
+      </c>
+      <c r="E252" s="4">
         <v>1</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19340,9 +20099,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>6</v>
+      </c>
+      <c r="E253" s="4">
         <v>2</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19426,9 +20188,12 @@
         </is>
       </c>
       <c r="D254" s="4">
+        <v>6</v>
+      </c>
+      <c r="E254" s="4">
         <v>3</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19504,9 +20269,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>6</v>
+      </c>
+      <c r="E255" s="4">
         <v>4</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19575,9 +20343,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>6</v>
+      </c>
+      <c r="E256" s="4">
         <v>5</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19648,7 +20419,10 @@
       <c r="D257" s="4">
         <v>6</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="E257" s="4">
+        <v>6</v>
+      </c>
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19711,7 +20485,10 @@
       <c r="D258" s="4">
         <v>1</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="E258" s="4">
+        <v>1</v>
+      </c>
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19772,9 +20549,12 @@
         </is>
       </c>
       <c r="D259" s="4">
+        <v>12</v>
+      </c>
+      <c r="E259" s="4">
         <v>1</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19844,9 +20624,12 @@
         </is>
       </c>
       <c r="D260" s="4">
+        <v>12</v>
+      </c>
+      <c r="E260" s="4">
         <v>2</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19907,9 +20690,12 @@
         </is>
       </c>
       <c r="D261" s="4">
+        <v>12</v>
+      </c>
+      <c r="E261" s="4">
         <v>3</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19979,9 +20765,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>12</v>
+      </c>
+      <c r="E262" s="4">
         <v>4</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20051,9 +20840,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>12</v>
+      </c>
+      <c r="E263" s="4">
         <v>5</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20123,9 +20915,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>12</v>
+      </c>
+      <c r="E264" s="4">
         <v>6</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20195,9 +20990,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>12</v>
+      </c>
+      <c r="E265" s="4">
         <v>7</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20267,9 +21065,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>12</v>
+      </c>
+      <c r="E266" s="4">
         <v>8</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20339,9 +21140,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>12</v>
+      </c>
+      <c r="E267" s="4">
         <v>9</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20411,9 +21215,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>12</v>
+      </c>
+      <c r="E268" s="4">
         <v>10</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20483,9 +21290,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>12</v>
+      </c>
+      <c r="E269" s="4">
         <v>11</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20557,7 +21367,10 @@
       <c r="D270" s="4">
         <v>12</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="E270" s="4">
+        <v>12</v>
+      </c>
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20618,9 +21431,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>16</v>
+      </c>
+      <c r="E271" s="4">
         <v>1</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20690,9 +21506,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>16</v>
+      </c>
+      <c r="E272" s="4">
         <v>2</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20762,9 +21581,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>16</v>
+      </c>
+      <c r="E273" s="4">
         <v>3</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20834,9 +21656,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>16</v>
+      </c>
+      <c r="E274" s="4">
         <v>4</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20906,9 +21731,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>16</v>
+      </c>
+      <c r="E275" s="4">
         <v>5</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20978,9 +21806,12 @@
         </is>
       </c>
       <c r="D276" s="4">
+        <v>16</v>
+      </c>
+      <c r="E276" s="4">
         <v>6</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21050,9 +21881,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>16</v>
+      </c>
+      <c r="E277" s="4">
         <v>7</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21122,9 +21956,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>16</v>
+      </c>
+      <c r="E278" s="4">
         <v>8</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21185,9 +22022,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>16</v>
+      </c>
+      <c r="E279" s="4">
         <v>9</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21257,9 +22097,12 @@
         </is>
       </c>
       <c r="D280" s="4">
+        <v>16</v>
+      </c>
+      <c r="E280" s="4">
         <v>10</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21329,9 +22172,12 @@
         </is>
       </c>
       <c r="D281" s="4">
+        <v>16</v>
+      </c>
+      <c r="E281" s="4">
         <v>11</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21401,9 +22247,12 @@
         </is>
       </c>
       <c r="D282" s="4">
+        <v>16</v>
+      </c>
+      <c r="E282" s="4">
         <v>12</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21473,9 +22322,12 @@
         </is>
       </c>
       <c r="D283" s="4">
+        <v>16</v>
+      </c>
+      <c r="E283" s="4">
         <v>13</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21545,9 +22397,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>16</v>
+      </c>
+      <c r="E284" s="4">
         <v>14</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21617,9 +22472,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>16</v>
+      </c>
+      <c r="E285" s="4">
         <v>15</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21691,7 +22549,10 @@
       <c r="D286" s="4">
         <v>16</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="E286" s="4">
+        <v>16</v>
+      </c>
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21752,9 +22613,12 @@
         </is>
       </c>
       <c r="D287" s="4">
+        <v>9</v>
+      </c>
+      <c r="E287" s="4">
         <v>1</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21808,9 +22672,12 @@
         </is>
       </c>
       <c r="D288" s="4">
+        <v>9</v>
+      </c>
+      <c r="E288" s="4">
         <v>2</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21864,9 +22731,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>9</v>
+      </c>
+      <c r="E289" s="4">
         <v>3</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21920,9 +22790,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>9</v>
+      </c>
+      <c r="E290" s="4">
         <v>4</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21976,9 +22849,12 @@
         </is>
       </c>
       <c r="D291" s="4">
+        <v>9</v>
+      </c>
+      <c r="E291" s="4">
         <v>5</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22032,9 +22908,12 @@
         </is>
       </c>
       <c r="D292" s="4">
+        <v>9</v>
+      </c>
+      <c r="E292" s="4">
         <v>6</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22088,9 +22967,12 @@
         </is>
       </c>
       <c r="D293" s="4">
+        <v>9</v>
+      </c>
+      <c r="E293" s="4">
         <v>7</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22144,9 +23026,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>9</v>
+      </c>
+      <c r="E294" s="4">
         <v>8</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22202,7 +23087,10 @@
       <c r="D295" s="4">
         <v>9</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="E295" s="4">
+        <v>9</v>
+      </c>
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22256,9 +23144,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>14</v>
+      </c>
+      <c r="E296" s="4">
         <v>1</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22312,9 +23203,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>14</v>
+      </c>
+      <c r="E297" s="4">
         <v>2</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22368,9 +23262,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>14</v>
+      </c>
+      <c r="E298" s="4">
         <v>3</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22424,9 +23321,12 @@
         </is>
       </c>
       <c r="D299" s="4">
+        <v>14</v>
+      </c>
+      <c r="E299" s="4">
         <v>4</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22480,9 +23380,12 @@
         </is>
       </c>
       <c r="D300" s="4">
+        <v>14</v>
+      </c>
+      <c r="E300" s="4">
         <v>5</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22536,9 +23439,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>14</v>
+      </c>
+      <c r="E301" s="4">
         <v>6</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22592,9 +23498,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>14</v>
+      </c>
+      <c r="E302" s="4">
         <v>7</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22648,9 +23557,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>14</v>
+      </c>
+      <c r="E303" s="4">
         <v>8</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22704,9 +23616,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>14</v>
+      </c>
+      <c r="E304" s="4">
         <v>9</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22760,9 +23675,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>14</v>
+      </c>
+      <c r="E305" s="4">
         <v>10</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22816,9 +23734,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>14</v>
+      </c>
+      <c r="E306" s="4">
         <v>11</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22872,9 +23793,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>14</v>
+      </c>
+      <c r="E307" s="4">
         <v>12</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22928,9 +23852,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>14</v>
+      </c>
+      <c r="E308" s="4">
         <v>13</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22986,7 +23913,10 @@
       <c r="D309" s="4">
         <v>14</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="E309" s="4">
+        <v>14</v>
+      </c>
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23040,9 +23970,12 @@
         </is>
       </c>
       <c r="D310" s="4">
+        <v>4</v>
+      </c>
+      <c r="E310" s="4">
         <v>1</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23096,9 +24029,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>4</v>
+      </c>
+      <c r="E311" s="4">
         <v>2</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23152,9 +24088,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>4</v>
+      </c>
+      <c r="E312" s="4">
         <v>3</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23210,7 +24149,10 @@
       <c r="D313" s="4">
         <v>4</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="E313" s="4">
+        <v>4</v>
+      </c>
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23264,9 +24206,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>3</v>
+      </c>
+      <c r="E314" s="4">
         <v>1</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23320,9 +24265,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>3</v>
+      </c>
+      <c r="E315" s="4">
         <v>2</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23378,7 +24326,10 @@
       <c r="D316" s="4">
         <v>3</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="E316" s="4">
+        <v>3</v>
+      </c>
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23432,9 +24383,12 @@
         </is>
       </c>
       <c r="D317" s="4">
+        <v>11</v>
+      </c>
+      <c r="E317" s="4">
         <v>1</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23488,9 +24442,12 @@
         </is>
       </c>
       <c r="D318" s="4">
+        <v>11</v>
+      </c>
+      <c r="E318" s="4">
         <v>2</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23544,9 +24501,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>11</v>
+      </c>
+      <c r="E319" s="4">
         <v>3</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23600,9 +24560,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>11</v>
+      </c>
+      <c r="E320" s="4">
         <v>4</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23656,9 +24619,12 @@
         </is>
       </c>
       <c r="D321" s="4">
+        <v>11</v>
+      </c>
+      <c r="E321" s="4">
         <v>5</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23712,9 +24678,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>11</v>
+      </c>
+      <c r="E322" s="4">
         <v>6</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23768,9 +24737,12 @@
         </is>
       </c>
       <c r="D323" s="4">
+        <v>11</v>
+      </c>
+      <c r="E323" s="4">
         <v>7</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23824,9 +24796,12 @@
         </is>
       </c>
       <c r="D324" s="4">
+        <v>11</v>
+      </c>
+      <c r="E324" s="4">
         <v>8</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23880,9 +24855,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>11</v>
+      </c>
+      <c r="E325" s="4">
         <v>9</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23936,9 +24914,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>11</v>
+      </c>
+      <c r="E326" s="4">
         <v>10</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23994,7 +24975,10 @@
       <c r="D327" s="4">
         <v>11</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="E327" s="4">
+        <v>11</v>
+      </c>
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24048,9 +25032,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>6</v>
+      </c>
+      <c r="E328" s="4">
         <v>1</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24120,9 +25107,12 @@
         </is>
       </c>
       <c r="D329" s="4">
+        <v>6</v>
+      </c>
+      <c r="E329" s="4">
         <v>2</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24192,9 +25182,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>6</v>
+      </c>
+      <c r="E330" s="4">
         <v>3</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24264,9 +25257,12 @@
         </is>
       </c>
       <c r="D331" s="4">
+        <v>6</v>
+      </c>
+      <c r="E331" s="4">
         <v>4</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24336,9 +25332,12 @@
         </is>
       </c>
       <c r="D332" s="4">
+        <v>6</v>
+      </c>
+      <c r="E332" s="4">
         <v>5</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24410,7 +25409,10 @@
       <c r="D333" s="4">
         <v>6</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="E333" s="4">
+        <v>6</v>
+      </c>
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24480,9 +25482,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>2</v>
+      </c>
+      <c r="E334" s="4">
         <v>1</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24575,7 +25580,10 @@
       <c r="D335" s="4">
         <v>2</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="E335" s="4">
+        <v>2</v>
+      </c>
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24661,7 +25669,10 @@
       <c r="D336" s="4">
         <v>1</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="E336" s="4">
+        <v>1</v>
+      </c>
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24724,7 +25735,10 @@
       <c r="D337" s="4">
         <v>1</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="E337" s="4">
+        <v>1</v>
+      </c>
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24793,9 +25807,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>18</v>
+      </c>
+      <c r="E338" s="4">
         <v>1</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24954,9 +25971,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>18</v>
+      </c>
+      <c r="E339" s="4">
         <v>2</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25070,9 +26090,12 @@
         </is>
       </c>
       <c r="D340" s="4">
+        <v>18</v>
+      </c>
+      <c r="E340" s="4">
         <v>3</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25178,9 +26201,12 @@
         </is>
       </c>
       <c r="D341" s="4">
+        <v>18</v>
+      </c>
+      <c r="E341" s="4">
         <v>4</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25279,9 +26305,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>18</v>
+      </c>
+      <c r="E342" s="4">
         <v>5</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25402,9 +26431,12 @@
         </is>
       </c>
       <c r="D343" s="4">
+        <v>18</v>
+      </c>
+      <c r="E343" s="4">
         <v>6</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25525,9 +26557,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>18</v>
+      </c>
+      <c r="E344" s="4">
         <v>7</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25671,9 +26706,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>18</v>
+      </c>
+      <c r="E345" s="4">
         <v>8</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25809,9 +26847,12 @@
         </is>
       </c>
       <c r="D346" s="4">
+        <v>18</v>
+      </c>
+      <c r="E346" s="4">
         <v>9</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25962,9 +27003,12 @@
         </is>
       </c>
       <c r="D347" s="4">
+        <v>18</v>
+      </c>
+      <c r="E347" s="4">
         <v>10</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26085,9 +27129,12 @@
         </is>
       </c>
       <c r="D348" s="4">
+        <v>18</v>
+      </c>
+      <c r="E348" s="4">
         <v>11</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26178,9 +27225,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>18</v>
+      </c>
+      <c r="E349" s="4">
         <v>12</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26376,9 +27426,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>18</v>
+      </c>
+      <c r="E350" s="4">
         <v>13</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26537,9 +27590,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>18</v>
+      </c>
+      <c r="E351" s="4">
         <v>14</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26690,9 +27746,12 @@
         </is>
       </c>
       <c r="D352" s="4">
+        <v>18</v>
+      </c>
+      <c r="E352" s="4">
         <v>15</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26806,9 +27865,12 @@
         </is>
       </c>
       <c r="D353" s="4">
+        <v>18</v>
+      </c>
+      <c r="E353" s="4">
         <v>16</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26959,9 +28021,12 @@
         </is>
       </c>
       <c r="D354" s="4">
+        <v>18</v>
+      </c>
+      <c r="E354" s="4">
         <v>17</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27099,7 +28164,10 @@
       <c r="D355" s="4">
         <v>18</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="E355" s="4">
+        <v>18</v>
+      </c>
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27245,7 +28313,10 @@
       <c r="D356" s="4">
         <v>1</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="E356" s="4">
+        <v>1</v>
+      </c>
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27317,7 +28388,10 @@
       <c r="D357" s="4">
         <v>1</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="E357" s="4">
+        <v>1</v>
+      </c>
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27403,7 +28477,10 @@
       <c r="D358" s="4">
         <v>1</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="E358" s="4">
+        <v>1</v>
+      </c>
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27466,7 +28543,10 @@
       <c r="D359" s="4">
         <v>1</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="E359" s="4">
+        <v>1</v>
+      </c>
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27589,7 +28669,10 @@
       <c r="D360" s="4">
         <v>1</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="E360" s="4">
+        <v>1</v>
+      </c>
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27661,7 +28744,10 @@
       <c r="D361" s="4">
         <v>1</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="E361" s="4">
+        <v>1</v>
+      </c>
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27739,7 +28825,10 @@
       <c r="D362" s="4">
         <v>1</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="E362" s="4">
+        <v>1</v>
+      </c>
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27802,7 +28891,10 @@
       <c r="D363" s="4">
         <v>1</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="E363" s="4">
+        <v>1</v>
+      </c>
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27871,9 +28963,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>7</v>
+      </c>
+      <c r="E364" s="4">
         <v>1</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28002,9 +29097,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>7</v>
+      </c>
+      <c r="E365" s="4">
         <v>2</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28140,9 +29238,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>7</v>
+      </c>
+      <c r="E366" s="4">
         <v>3</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28241,9 +29342,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>7</v>
+      </c>
+      <c r="E367" s="4">
         <v>4</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28349,9 +29453,12 @@
         </is>
       </c>
       <c r="D368" s="4">
+        <v>7</v>
+      </c>
+      <c r="E368" s="4">
         <v>5</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28532,9 +29639,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>7</v>
+      </c>
+      <c r="E369" s="4">
         <v>6</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28665,7 +29775,10 @@
       <c r="D370" s="4">
         <v>7</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="E370" s="4">
+        <v>7</v>
+      </c>
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28764,9 +29877,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>3</v>
+      </c>
+      <c r="E371" s="4">
         <v>1</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28827,9 +29943,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>3</v>
+      </c>
+      <c r="E372" s="4">
         <v>2</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28915,7 +30034,10 @@
       <c r="D373" s="4">
         <v>3</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="E373" s="4">
+        <v>3</v>
+      </c>
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29006,9 +30128,12 @@
         </is>
       </c>
       <c r="D374" s="4">
+        <v>10</v>
+      </c>
+      <c r="E374" s="4">
         <v>1</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29069,9 +30194,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>10</v>
+      </c>
+      <c r="E375" s="4">
         <v>2</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29132,9 +30260,12 @@
         </is>
       </c>
       <c r="D376" s="4">
+        <v>10</v>
+      </c>
+      <c r="E376" s="4">
         <v>3</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29195,9 +30326,12 @@
         </is>
       </c>
       <c r="D377" s="4">
+        <v>10</v>
+      </c>
+      <c r="E377" s="4">
         <v>4</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29258,9 +30392,12 @@
         </is>
       </c>
       <c r="D378" s="4">
+        <v>10</v>
+      </c>
+      <c r="E378" s="4">
         <v>5</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29321,9 +30458,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>10</v>
+      </c>
+      <c r="E379" s="4">
         <v>6</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29384,9 +30524,12 @@
         </is>
       </c>
       <c r="D380" s="4">
+        <v>10</v>
+      </c>
+      <c r="E380" s="4">
         <v>7</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29447,9 +30590,12 @@
         </is>
       </c>
       <c r="D381" s="4">
+        <v>10</v>
+      </c>
+      <c r="E381" s="4">
         <v>8</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29510,9 +30656,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>10</v>
+      </c>
+      <c r="E382" s="4">
         <v>9</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29575,7 +30724,10 @@
       <c r="D383" s="4">
         <v>1</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="E383" s="4">
+        <v>1</v>
+      </c>
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29644,9 +30796,12 @@
         </is>
       </c>
       <c r="D384" s="4">
+        <v>9</v>
+      </c>
+      <c r="E384" s="4">
         <v>1</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29707,9 +30862,12 @@
         </is>
       </c>
       <c r="D385" s="4">
+        <v>9</v>
+      </c>
+      <c r="E385" s="4">
         <v>2</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29793,9 +30951,12 @@
         </is>
       </c>
       <c r="D386" s="4">
+        <v>9</v>
+      </c>
+      <c r="E386" s="4">
         <v>3</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29894,9 +31055,12 @@
         </is>
       </c>
       <c r="D387" s="4">
+        <v>9</v>
+      </c>
+      <c r="E387" s="4">
         <v>4</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29957,9 +31121,12 @@
         </is>
       </c>
       <c r="D388" s="4">
+        <v>9</v>
+      </c>
+      <c r="E388" s="4">
         <v>5</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30035,9 +31202,12 @@
         </is>
       </c>
       <c r="D389" s="4">
+        <v>9</v>
+      </c>
+      <c r="E389" s="4">
         <v>6</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30098,9 +31268,12 @@
         </is>
       </c>
       <c r="D390" s="4">
+        <v>9</v>
+      </c>
+      <c r="E390" s="4">
         <v>7</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30191,9 +31364,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>9</v>
+      </c>
+      <c r="E391" s="4">
         <v>8</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30264,7 +31440,10 @@
       <c r="D392" s="4">
         <v>9</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="E392" s="4">
+        <v>9</v>
+      </c>
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30325,9 +31504,12 @@
         </is>
       </c>
       <c r="D393" s="4">
+        <v>6</v>
+      </c>
+      <c r="E393" s="4">
         <v>1</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30397,9 +31579,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>6</v>
+      </c>
+      <c r="E394" s="4">
         <v>2</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30469,9 +31654,12 @@
         </is>
       </c>
       <c r="D395" s="4">
+        <v>6</v>
+      </c>
+      <c r="E395" s="4">
         <v>3</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30541,9 +31729,12 @@
         </is>
       </c>
       <c r="D396" s="4">
+        <v>6</v>
+      </c>
+      <c r="E396" s="4">
         <v>4</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30613,9 +31804,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>6</v>
+      </c>
+      <c r="E397" s="4">
         <v>5</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30687,7 +31881,10 @@
       <c r="D398" s="4">
         <v>6</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="E398" s="4">
+        <v>6</v>
+      </c>
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30757,9 +31954,12 @@
         </is>
       </c>
       <c r="D399" s="4">
+        <v>3</v>
+      </c>
+      <c r="E399" s="4">
         <v>1</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30829,9 +32029,12 @@
         </is>
       </c>
       <c r="D400" s="4">
+        <v>3</v>
+      </c>
+      <c r="E400" s="4">
         <v>2</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30903,7 +32106,10 @@
       <c r="D401" s="4">
         <v>3</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="E401" s="4">
+        <v>3</v>
+      </c>
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30973,9 +32179,12 @@
         </is>
       </c>
       <c r="D402" s="4">
+        <v>5</v>
+      </c>
+      <c r="E402" s="4">
         <v>1</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31036,9 +32245,12 @@
         </is>
       </c>
       <c r="D403" s="4">
+        <v>5</v>
+      </c>
+      <c r="E403" s="4">
         <v>2</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31108,9 +32320,12 @@
         </is>
       </c>
       <c r="D404" s="4">
+        <v>5</v>
+      </c>
+      <c r="E404" s="4">
         <v>3</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31180,9 +32395,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>5</v>
+      </c>
+      <c r="E405" s="4">
         <v>4</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31254,7 +32472,10 @@
       <c r="D406" s="4">
         <v>5</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="E406" s="4">
+        <v>5</v>
+      </c>
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31326,7 +32547,10 @@
       <c r="D407" s="4">
         <v>1</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="E407" s="4">
+        <v>1</v>
+      </c>
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31396,9 +32620,12 @@
         </is>
       </c>
       <c r="D408" s="4">
+        <v>2</v>
+      </c>
+      <c r="E408" s="4">
         <v>1</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31470,7 +32697,10 @@
       <c r="D409" s="4">
         <v>2</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="E409" s="4">
+        <v>2</v>
+      </c>
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31542,7 +32772,10 @@
       <c r="D410" s="4">
         <v>1</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="E410" s="4">
+        <v>1</v>
+      </c>
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31614,7 +32847,10 @@
       <c r="D411" s="4">
         <v>1</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="E411" s="4">
+        <v>1</v>
+      </c>
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31686,7 +32922,10 @@
       <c r="D412" s="4">
         <v>1</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="E412" s="4">
+        <v>1</v>
+      </c>
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31747,9 +32986,12 @@
         </is>
       </c>
       <c r="D413" s="4">
+        <v>5</v>
+      </c>
+      <c r="E413" s="4">
         <v>1</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31819,9 +33061,12 @@
         </is>
       </c>
       <c r="D414" s="4">
+        <v>5</v>
+      </c>
+      <c r="E414" s="4">
         <v>2</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31891,9 +33136,12 @@
         </is>
       </c>
       <c r="D415" s="4">
+        <v>5</v>
+      </c>
+      <c r="E415" s="4">
         <v>3</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31963,9 +33211,12 @@
         </is>
       </c>
       <c r="D416" s="4">
+        <v>5</v>
+      </c>
+      <c r="E416" s="4">
         <v>4</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32035,9 +33286,12 @@
         </is>
       </c>
       <c r="D417" s="4">
+        <v>3</v>
+      </c>
+      <c r="E417" s="4">
         <v>1</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32107,9 +33361,12 @@
         </is>
       </c>
       <c r="D418" s="4">
+        <v>3</v>
+      </c>
+      <c r="E418" s="4">
         <v>2</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32181,7 +33438,10 @@
       <c r="D419" s="4">
         <v>3</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="E419" s="4">
+        <v>3</v>
+      </c>
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32251,9 +33511,12 @@
         </is>
       </c>
       <c r="D420" s="4">
+        <v>7</v>
+      </c>
+      <c r="E420" s="4">
         <v>1</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32323,9 +33586,12 @@
         </is>
       </c>
       <c r="D421" s="4">
+        <v>7</v>
+      </c>
+      <c r="E421" s="4">
         <v>2</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32395,9 +33661,12 @@
         </is>
       </c>
       <c r="D422" s="4">
+        <v>7</v>
+      </c>
+      <c r="E422" s="4">
         <v>3</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32467,9 +33736,12 @@
         </is>
       </c>
       <c r="D423" s="4">
+        <v>7</v>
+      </c>
+      <c r="E423" s="4">
         <v>4</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32539,9 +33811,12 @@
         </is>
       </c>
       <c r="D424" s="4">
+        <v>7</v>
+      </c>
+      <c r="E424" s="4">
         <v>5</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32611,9 +33886,12 @@
         </is>
       </c>
       <c r="D425" s="4">
+        <v>7</v>
+      </c>
+      <c r="E425" s="4">
         <v>6</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32685,7 +33963,10 @@
       <c r="D426" s="4">
         <v>7</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="E426" s="4">
+        <v>7</v>
+      </c>
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32755,9 +34036,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>2</v>
+      </c>
+      <c r="E427" s="4">
         <v>1</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32829,7 +34113,10 @@
       <c r="D428" s="4">
         <v>2</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="E428" s="4">
+        <v>2</v>
+      </c>
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32901,7 +34188,10 @@
       <c r="D429" s="4">
         <v>1</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="E429" s="4">
+        <v>1</v>
+      </c>
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32971,9 +34261,12 @@
         </is>
       </c>
       <c r="D430" s="4">
+        <v>3</v>
+      </c>
+      <c r="E430" s="4">
         <v>1</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33043,9 +34336,12 @@
         </is>
       </c>
       <c r="D431" s="4">
+        <v>3</v>
+      </c>
+      <c r="E431" s="4">
         <v>2</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33117,7 +34413,10 @@
       <c r="D432" s="4">
         <v>3</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="E432" s="4">
+        <v>3</v>
+      </c>
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33171,193 +34470,255 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="186">
+  <mergeCells count="248">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
     <mergeCell ref="A21:A23"/>
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="C24:C25"/>
+    <mergeCell ref="D24:D25"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="B32:B33"/>
     <mergeCell ref="C32:C33"/>
+    <mergeCell ref="D32:D33"/>
     <mergeCell ref="A41:A43"/>
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="C41:C43"/>
+    <mergeCell ref="D41:D43"/>
     <mergeCell ref="A46:A48"/>
     <mergeCell ref="B46:B48"/>
     <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
     <mergeCell ref="A56:A58"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="C56:C58"/>
+    <mergeCell ref="D56:D58"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="B67:B68"/>
     <mergeCell ref="C67:C68"/>
+    <mergeCell ref="D67:D68"/>
     <mergeCell ref="A88:A92"/>
     <mergeCell ref="B88:B92"/>
     <mergeCell ref="C88:C92"/>
+    <mergeCell ref="D88:D92"/>
     <mergeCell ref="A94:A98"/>
     <mergeCell ref="B94:B98"/>
     <mergeCell ref="C94:C98"/>
+    <mergeCell ref="D94:D98"/>
     <mergeCell ref="A104:A105"/>
     <mergeCell ref="B104:B105"/>
     <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
     <mergeCell ref="A113:A115"/>
     <mergeCell ref="B113:B115"/>
     <mergeCell ref="C113:C115"/>
+    <mergeCell ref="D113:D115"/>
     <mergeCell ref="A119:A120"/>
     <mergeCell ref="B119:B120"/>
     <mergeCell ref="C119:C120"/>
+    <mergeCell ref="D119:D120"/>
     <mergeCell ref="A131:A132"/>
     <mergeCell ref="B131:B132"/>
     <mergeCell ref="C131:C132"/>
+    <mergeCell ref="D131:D132"/>
     <mergeCell ref="A134:A135"/>
     <mergeCell ref="B134:B135"/>
     <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:D135"/>
     <mergeCell ref="A136:A138"/>
     <mergeCell ref="B136:B138"/>
     <mergeCell ref="C136:C138"/>
+    <mergeCell ref="D136:D138"/>
     <mergeCell ref="A141:A142"/>
     <mergeCell ref="B141:B142"/>
     <mergeCell ref="C141:C142"/>
+    <mergeCell ref="D141:D142"/>
     <mergeCell ref="A145:A146"/>
     <mergeCell ref="B145:B146"/>
     <mergeCell ref="C145:C146"/>
+    <mergeCell ref="D145:D146"/>
     <mergeCell ref="A154:A155"/>
     <mergeCell ref="B154:B155"/>
     <mergeCell ref="C154:C155"/>
+    <mergeCell ref="D154:D155"/>
     <mergeCell ref="A158:A160"/>
     <mergeCell ref="B158:B160"/>
     <mergeCell ref="C158:C160"/>
+    <mergeCell ref="D158:D160"/>
     <mergeCell ref="A162:A163"/>
     <mergeCell ref="B162:B163"/>
     <mergeCell ref="C162:C163"/>
+    <mergeCell ref="D162:D163"/>
     <mergeCell ref="A164:A168"/>
     <mergeCell ref="B164:B168"/>
     <mergeCell ref="C164:C168"/>
+    <mergeCell ref="D164:D168"/>
     <mergeCell ref="A177:A178"/>
     <mergeCell ref="B177:B178"/>
     <mergeCell ref="C177:C178"/>
+    <mergeCell ref="D177:D178"/>
     <mergeCell ref="A180:A182"/>
     <mergeCell ref="B180:B182"/>
     <mergeCell ref="C180:C182"/>
+    <mergeCell ref="D180:D182"/>
     <mergeCell ref="A186:A188"/>
     <mergeCell ref="B186:B188"/>
     <mergeCell ref="C186:C188"/>
+    <mergeCell ref="D186:D188"/>
     <mergeCell ref="A194:A198"/>
     <mergeCell ref="B194:B198"/>
     <mergeCell ref="C194:C198"/>
+    <mergeCell ref="D194:D198"/>
     <mergeCell ref="A199:A200"/>
     <mergeCell ref="B199:B200"/>
     <mergeCell ref="C199:C200"/>
+    <mergeCell ref="D199:D200"/>
     <mergeCell ref="A203:A208"/>
     <mergeCell ref="B203:B208"/>
     <mergeCell ref="C203:C208"/>
+    <mergeCell ref="D203:D208"/>
     <mergeCell ref="A209:A211"/>
     <mergeCell ref="B209:B211"/>
     <mergeCell ref="C209:C211"/>
+    <mergeCell ref="D209:D211"/>
     <mergeCell ref="A212:A231"/>
     <mergeCell ref="B212:B231"/>
     <mergeCell ref="C212:C231"/>
+    <mergeCell ref="D212:D231"/>
     <mergeCell ref="A232:A233"/>
     <mergeCell ref="B232:B233"/>
     <mergeCell ref="C232:C233"/>
+    <mergeCell ref="D232:D233"/>
     <mergeCell ref="A234:A237"/>
     <mergeCell ref="B234:B237"/>
     <mergeCell ref="C234:C237"/>
+    <mergeCell ref="D234:D237"/>
     <mergeCell ref="A241:A243"/>
     <mergeCell ref="B241:B243"/>
     <mergeCell ref="C241:C243"/>
+    <mergeCell ref="D241:D243"/>
     <mergeCell ref="A245:A246"/>
     <mergeCell ref="B245:B246"/>
     <mergeCell ref="C245:C246"/>
+    <mergeCell ref="D245:D246"/>
     <mergeCell ref="A248:A250"/>
     <mergeCell ref="B248:B250"/>
     <mergeCell ref="C248:C250"/>
+    <mergeCell ref="D248:D250"/>
     <mergeCell ref="A252:A257"/>
     <mergeCell ref="B252:B257"/>
     <mergeCell ref="C252:C257"/>
+    <mergeCell ref="D252:D257"/>
     <mergeCell ref="A259:A270"/>
     <mergeCell ref="B259:B270"/>
     <mergeCell ref="C259:C270"/>
+    <mergeCell ref="D259:D270"/>
     <mergeCell ref="A271:A286"/>
     <mergeCell ref="B271:B286"/>
     <mergeCell ref="C271:C286"/>
+    <mergeCell ref="D271:D286"/>
     <mergeCell ref="A287:A295"/>
     <mergeCell ref="B287:B295"/>
     <mergeCell ref="C287:C295"/>
+    <mergeCell ref="D287:D295"/>
     <mergeCell ref="A296:A309"/>
     <mergeCell ref="B296:B309"/>
     <mergeCell ref="C296:C309"/>
+    <mergeCell ref="D296:D309"/>
     <mergeCell ref="A310:A313"/>
     <mergeCell ref="B310:B313"/>
     <mergeCell ref="C310:C313"/>
+    <mergeCell ref="D310:D313"/>
     <mergeCell ref="A314:A316"/>
     <mergeCell ref="B314:B316"/>
     <mergeCell ref="C314:C316"/>
+    <mergeCell ref="D314:D316"/>
     <mergeCell ref="A317:A327"/>
     <mergeCell ref="B317:B327"/>
     <mergeCell ref="C317:C327"/>
+    <mergeCell ref="D317:D327"/>
     <mergeCell ref="A328:A333"/>
     <mergeCell ref="B328:B333"/>
     <mergeCell ref="C328:C333"/>
+    <mergeCell ref="D328:D333"/>
     <mergeCell ref="A334:A335"/>
     <mergeCell ref="B334:B335"/>
     <mergeCell ref="C334:C335"/>
+    <mergeCell ref="D334:D335"/>
     <mergeCell ref="A338:A355"/>
     <mergeCell ref="B338:B355"/>
     <mergeCell ref="C338:C355"/>
+    <mergeCell ref="D338:D355"/>
     <mergeCell ref="A364:A370"/>
     <mergeCell ref="B364:B370"/>
     <mergeCell ref="C364:C370"/>
+    <mergeCell ref="D364:D370"/>
     <mergeCell ref="A371:A373"/>
     <mergeCell ref="B371:B373"/>
     <mergeCell ref="C371:C373"/>
+    <mergeCell ref="D371:D373"/>
     <mergeCell ref="A374:A382"/>
     <mergeCell ref="B374:B382"/>
     <mergeCell ref="C374:C382"/>
+    <mergeCell ref="D374:D382"/>
     <mergeCell ref="A384:A392"/>
     <mergeCell ref="B384:B392"/>
     <mergeCell ref="C384:C392"/>
+    <mergeCell ref="D384:D392"/>
     <mergeCell ref="A393:A398"/>
     <mergeCell ref="B393:B398"/>
     <mergeCell ref="C393:C398"/>
+    <mergeCell ref="D393:D398"/>
     <mergeCell ref="A399:A401"/>
     <mergeCell ref="B399:B401"/>
     <mergeCell ref="C399:C401"/>
+    <mergeCell ref="D399:D401"/>
     <mergeCell ref="A402:A406"/>
     <mergeCell ref="B402:B406"/>
     <mergeCell ref="C402:C406"/>
+    <mergeCell ref="D402:D406"/>
     <mergeCell ref="A408:A409"/>
     <mergeCell ref="B408:B409"/>
     <mergeCell ref="C408:C409"/>
+    <mergeCell ref="D408:D409"/>
     <mergeCell ref="A413:A416"/>
     <mergeCell ref="B413:B416"/>
     <mergeCell ref="C413:C416"/>
+    <mergeCell ref="D413:D416"/>
     <mergeCell ref="A417:A419"/>
     <mergeCell ref="B417:B419"/>
     <mergeCell ref="C417:C419"/>
+    <mergeCell ref="D417:D419"/>
     <mergeCell ref="A420:A426"/>
     <mergeCell ref="B420:B426"/>
     <mergeCell ref="C420:C426"/>
+    <mergeCell ref="D420:D426"/>
     <mergeCell ref="A427:A428"/>
     <mergeCell ref="B427:B428"/>
     <mergeCell ref="C427:C428"/>
+    <mergeCell ref="D427:D428"/>
     <mergeCell ref="A430:A432"/>
     <mergeCell ref="B430:B432"/>
     <mergeCell ref="C430:C432"/>
+    <mergeCell ref="D430:D432"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
